--- a/reports/Debug-snowbowl-20251216/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Week Ending (Prior Year)_Visits.xlsx
@@ -31,16 +31,16 @@
     <t>Snowbowl</t>
   </si>
   <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
     <t>Snowbowl Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
         <v>45642</v>
       </c>
       <c r="C2" s="2">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>45642</v>
       </c>
       <c r="C3" s="2">
-        <v>602</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,7 +462,7 @@
         <v>45642</v>
       </c>
       <c r="C4" s="2">
-        <v>83</v>
+        <v>602</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -473,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="C5" s="2">
-        <v>523</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,7 +490,7 @@
         <v>45642</v>
       </c>
       <c r="C6" s="2">
-        <v>19</v>
+        <v>1096</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
@@ -504,10 +504,10 @@
         <v>45643</v>
       </c>
       <c r="C7" s="2">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,7 +518,7 @@
         <v>45643</v>
       </c>
       <c r="C8" s="2">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="C9" s="2">
-        <v>71</v>
+        <v>523</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="C10" s="2">
-        <v>1155</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -560,10 +560,10 @@
         <v>45643</v>
       </c>
       <c r="C11" s="2">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,10 +588,10 @@
         <v>45642</v>
       </c>
       <c r="C13" s="2">
-        <v>1096</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +602,10 @@
         <v>45643</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>1155</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>45643</v>
       </c>
       <c r="C15" s="2">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
